--- a/out/LSTM-Mamba1_repeat_4_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8927231521932764</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.60677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.00677127013091</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_4_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.6448742778844246</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>3.60677127013091</v>
+        <v>1.536187288701382</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.60677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.00677127013091</v>
+        <v>2.427500299518339</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.00677127013091</v>
+        <v>2.227500299518339</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.00677127013091</v>
+        <v>1.336187288701382</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8927231521932764</v>
+        <v>0.4448742778844246</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8927231521932764</v>
+        <v>-0.4464387329325323</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_4_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.00198090192861855</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001245629275217652</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.000792764825746417</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0005088134203106165</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0003290162421762943</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.16</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.000220203772187233</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0001558840740472078</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0001140357926487923</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-9.277602657675743e-05</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-9.777070954442024e-05</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-9.627989493310452e-05</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-9.07254870980978e-05</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-7.97477550804615e-05</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-7.553491741418839e-05</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-6.988109089434147e-05</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-6.20703212916851e-05</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-4.733819514513016e-05</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-2.964097075164318e-05</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-1.020100899040699e-05</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6448742778844246</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>6.683403626084328e-06</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.536187288701382</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>1.916149631142616e-05</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>3.616185858845711e-05</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>5.40523324161768e-05</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>7.233885116875172e-05</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>6.25185202807188e-05</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.427500299518339</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>5.379784852266312e-05</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.427500299518339</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>4.440289922058582e-05</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.427500299518339</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>3.513484261929989e-05</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.427500299518339</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>2.675107680261135e-05</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.427500299518339</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>2.783979289233685e-05</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>3.732810728251934e-05</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.227500299518339</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>4.84958291053772e-05</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.227500299518339</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>5.728378891944885e-05</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.227500299518339</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>6.392807699739933e-05</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.227500299518339</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>6.843847222626209e-05</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.227500299518339</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>6.286776624619961e-05</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.227500299518339</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>4.03313897550106e-05</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.227500299518339</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>8.724397048354149e-06</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.336187288701382</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-1.794565469026566e-05</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.4448742778844246</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-5.167466588318348e-05</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-9.149312973022461e-05</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0001808288507163525</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0003312868066132069</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.0004906572867184877</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.000640001380816102</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.000702231889590621</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0007216548547148705</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0007301152218133211</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.0007330679800361395</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0007375022396445274</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0007675352972000837</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0007640765979886055</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0007598872762173414</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.000749615952372551</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0007405828218907118</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0007332812529057264</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0007211132906377316</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0007101630326360464</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0007121444214135408</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.000708400271832943</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.000704397214576602</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0007065094541758299</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0007017638999968767</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.0006944744382053614</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0006999755278229713</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0007198022212833166</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0007622120901942253</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0007787006907165051</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0007752829696983099</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0007558164652436972</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.0007339422591030598</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0007022724021226168</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0006684781983494759</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0006407834589481354</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.0006188845727592707</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.0006012131925672293</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0005808428395539522</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0005527492612600327</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.0005270778201520443</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.0005058730021119118</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.0004962291568517685</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.0004939129576086998</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0005014757625758648</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.0005141966976225376</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.0005252552218735218</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.0005254843272268772</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.16</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.0005224565975368023</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.0005213601980358362</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.0005243935156613588</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.0005289120599627495</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.0005344201344996691</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.16</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.0005323376972228289</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.0005195036064833403</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.0004970771260559559</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0004730145446956158</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0004407335072755814</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.0004098783247172832</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.0003786701709032059</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.0003500252496451139</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.0003242716193199158</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.000300949439406395</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.000281238229945302</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.000262740533798933</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.0002432314213365316</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.0002194102853536606</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.0001928829587996006</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.0001654683146625757</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.0001438583713024855</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.0001278005074709654</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0001157063525170088</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.0001006536185741425</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-7.835053838789463e-05</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-6.499909795820713e-05</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-6.320676766335964e-05</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-6.459746509790421e-05</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-4.370557144284248e-05</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-2.918299287557602e-05</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-2.73585319519043e-05</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-6.124330684542656e-05</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4464387329325323</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-8.787494152784348e-05</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.0001255131792277098</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.16</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.000156014459207654</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.0001578782685101032</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.0001492428127676249</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0001412020064890385</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4464387329325323</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_4_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_4_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.00198090192861855</v>
+        <v>-0.001980900298804045</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.001245629275217652</v>
+        <v>-0.001245628343895078</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0003290162421762943</v>
+        <v>-0.0003290087915956974</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.16</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.000220203772187233</v>
+        <v>-0.0002202002797275782</v>
       </c>
       <c r="JB7" t="n">
         <v>0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0001558840740472078</v>
+        <v>-0.000155874527990818</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0001140357926487923</v>
+        <v>-0.0001140239182859659</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-9.277602657675743e-05</v>
+        <v>-9.277043864130974e-05</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-9.777070954442024e-05</v>
+        <v>-9.777047671377659e-05</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-9.627989493310452e-05</v>
+        <v>-9.627942927181721e-05</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-9.07254870980978e-05</v>
+        <v>-9.071826934814453e-05</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-7.97477550804615e-05</v>
+        <v>-7.974612526595592e-05</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-7.553491741418839e-05</v>
+        <v>-7.552583701908588e-05</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-6.988109089434147e-05</v>
+        <v>-6.987806409597397e-05</v>
       </c>
       <c r="JB16" t="n">
         <v>0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-6.20703212916851e-05</v>
+        <v>-6.207707338035107e-05</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-4.733819514513016e-05</v>
+        <v>-4.734122194349766e-05</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-2.964097075164318e-05</v>
+        <v>-2.964376471936703e-05</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-1.020100899040699e-05</v>
+        <v>-1.020263880491257e-05</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>6.683403626084328e-06</v>
+        <v>6.681540980935097e-06</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3999999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1.916149631142616e-05</v>
+        <v>1.917057670652866e-05</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3999999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>3.616185858845711e-05</v>
+        <v>3.616535104811192e-05</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3999999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>5.40523324161768e-05</v>
+        <v>5.405326373875141e-05</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3999999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>7.233885116875172e-05</v>
+        <v>7.233838550746441e-05</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3999999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>6.25185202807188e-05</v>
+        <v>6.252131424844265e-05</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3999999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>5.379784852266312e-05</v>
+        <v>5.379877984523773e-05</v>
       </c>
       <c r="JB27" t="n">
         <v>0.2599999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>4.440289922058582e-05</v>
+        <v>4.440476186573505e-05</v>
       </c>
       <c r="JB28" t="n">
         <v>0.1199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>3.513484261929989e-05</v>
+        <v>3.51383350789547e-05</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.02000000000000007</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>2.675107680261135e-05</v>
+        <v>2.6751309633255e-05</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>2.783979289233685e-05</v>
+        <v>2.783909440040588e-05</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.16</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>4.84958291053772e-05</v>
+        <v>4.850211553275585e-05</v>
       </c>
       <c r="JB33" t="n">
         <v>0.1199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>5.728378891944885e-05</v>
+        <v>5.729426629841328e-05</v>
       </c>
       <c r="JB34" t="n">
         <v>0.2599999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>6.392807699739933e-05</v>
+        <v>6.393366493284702e-05</v>
       </c>
       <c r="JB35" t="n">
         <v>0.9999999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>6.843847222626209e-05</v>
+        <v>6.844126619398594e-05</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>6.286776624619961e-05</v>
+        <v>6.286799907684326e-05</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>4.03313897550106e-05</v>
+        <v>4.033208824694157e-05</v>
       </c>
       <c r="JB38" t="n">
         <v>0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>8.724397048354149e-06</v>
+        <v>8.725561201572418e-06</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-1.794565469026566e-05</v>
+        <v>-1.794658601284027e-05</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-5.167466588318348e-05</v>
+        <v>-5.167536437511444e-05</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-9.149312973022461e-05</v>
+        <v>-9.149126708507538e-05</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.0001808288507163525</v>
+        <v>-0.0001808218657970428</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0003312868066132069</v>
+        <v>-0.0003312812186777592</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.0004906572867184877</v>
+        <v>-0.0004906542599201202</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.000640001380816102</v>
+        <v>-0.0006399985868483782</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.000702231889590621</v>
+        <v>-0.0007022293284535408</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0007216548547148705</v>
+        <v>-0.0007216539233922958</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0007301152218133211</v>
+        <v>-0.0007301149889826775</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.0007330679800361395</v>
+        <v>-0.0007330693770200014</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0007375022396445274</v>
+        <v>-0.0007375057321041822</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0007675352972000837</v>
+        <v>-0.0007675392553210258</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.0007640765979886055</v>
+        <v>-0.0007640786934643984</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0007598872762173414</v>
+        <v>-0.0007598898373544216</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.000749615952372551</v>
+        <v>-0.0007496189791709185</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0007405828218907118</v>
+        <v>-0.0007405842188745737</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0007332812529057264</v>
+        <v>-0.000733282184228301</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.0007211132906377316</v>
+        <v>-0.0007211142219603062</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.0007101630326360464</v>
+        <v>-0.000710163963958621</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0007121444214135408</v>
+        <v>-0.0007121437229216099</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.000708400271832943</v>
+        <v>-0.0007084009703248739</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.000704397214576602</v>
+        <v>-0.0007043986115604639</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.0007065094541758299</v>
+        <v>-0.0007065115496516228</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0007017638999968767</v>
+        <v>-0.0007017657626420259</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.0006944744382053614</v>
+        <v>-0.0006944763008505106</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0006999755278229713</v>
+        <v>-0.0006999778561294079</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.0007198022212833166</v>
+        <v>-0.0007197996601462364</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.0007622120901942253</v>
+        <v>-0.0007622125558555126</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0007787006907165051</v>
+        <v>-0.0007787009235471487</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0007752829696983099</v>
+        <v>-0.0007752857636660337</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.0007558164652436972</v>
+        <v>-0.0007558185607194901</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.2599999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.0007339422591030598</v>
+        <v>-0.0007339459843933582</v>
       </c>
       <c r="JB72" t="n">
         <v>0.02000000000000007</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.0007022724021226168</v>
+        <v>-0.0007022740319371223</v>
       </c>
       <c r="JB73" t="n">
         <v>0.3</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.0006684781983494759</v>
+        <v>-0.0006684795953333378</v>
       </c>
       <c r="JB74" t="n">
         <v>0.5799999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.0006188845727592707</v>
+        <v>-0.0006188834086060524</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.0006012131925672293</v>
+        <v>-0.000601212028414011</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.0005808428395539522</v>
+        <v>-0.0005808433052152395</v>
       </c>
       <c r="JB78" t="n">
         <v>0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.0005527492612600327</v>
+        <v>-0.0005527494940906763</v>
       </c>
       <c r="JB79" t="n">
         <v>0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.0005270778201520443</v>
+        <v>-0.0005270771216601133</v>
       </c>
       <c r="JB80" t="n">
         <v>0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.0004962291568517685</v>
+        <v>-0.000496226828545332</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.0004939129576086998</v>
+        <v>-0.0004939122591167688</v>
       </c>
       <c r="JB83" t="n">
         <v>0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.0005014757625758648</v>
+        <v>-0.0005014752969145775</v>
       </c>
       <c r="JB84" t="n">
         <v>0.2599999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.0005141966976225376</v>
+        <v>-0.000514196464791894</v>
       </c>
       <c r="JB85" t="n">
         <v>0.1199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.0005252552218735218</v>
+        <v>-0.0005252566188573837</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.02000000000000007</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.0005254843272268772</v>
+        <v>-0.0005254854913800955</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.0005224565975368023</v>
+        <v>-0.000522456131875515</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.0005213601980358362</v>
+        <v>-0.0005213604308664799</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.0005243935156613588</v>
+        <v>-0.0005243953783065081</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.0005289120599627495</v>
+        <v>-0.0005289132241159678</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.0005344201344996691</v>
+        <v>-0.0005344238597899675</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.16</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.0005323376972228289</v>
+        <v>-0.0005323390942066908</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.02000000000000007</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.0005195036064833403</v>
+        <v>-0.0005194989498704672</v>
       </c>
       <c r="JB94" t="n">
         <v>0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.0004970771260559559</v>
+        <v>-0.0004970745649188757</v>
       </c>
       <c r="JB95" t="n">
         <v>0.8599999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.0004730145446956158</v>
+        <v>-0.0004730143118649721</v>
       </c>
       <c r="JB96" t="n">
         <v>0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.0004407335072755814</v>
+        <v>-0.0004407332744449377</v>
       </c>
       <c r="JB97" t="n">
         <v>0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.0004098783247172832</v>
+        <v>-0.0004098776262253523</v>
       </c>
       <c r="JB98" t="n">
         <v>0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.0003786701709032059</v>
+        <v>-0.0003786699380725622</v>
       </c>
       <c r="JB99" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.0003242716193199158</v>
+        <v>-0.0003242730163037777</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.000300949439406395</v>
+        <v>-0.000300941988825798</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.000281238229945302</v>
+        <v>-0.0002812331076711416</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.000262740533798933</v>
+        <v>-0.0002627286594361067</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.0002432314213365316</v>
+        <v>-0.0002432262990623713</v>
       </c>
       <c r="JB105" t="n">
         <v>0.3999999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.0002194102853536606</v>
+        <v>-0.0002194074913859367</v>
       </c>
       <c r="JB106" t="n">
         <v>0.3999999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.0001654683146625757</v>
+        <v>-0.0001654692459851503</v>
       </c>
       <c r="JB108" t="n">
         <v>0.3999999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.0001438583713024855</v>
+        <v>-0.0001438576728105545</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3999999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.0001278005074709654</v>
+        <v>-0.0001277998089790344</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3999999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.0001157063525170088</v>
+        <v>-0.0001157051883637905</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3999999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.0001006536185741425</v>
+        <v>-0.0001006545498967171</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-7.835053838789463e-05</v>
+        <v>-7.83517025411129e-05</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3999999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-6.499909795820713e-05</v>
+        <v>-6.499979645013809e-05</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3999999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-6.320676766335964e-05</v>
+        <v>-6.320560351014137e-05</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-6.459746509790421e-05</v>
+        <v>-6.459560245275497e-05</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-4.370557144284248e-05</v>
+        <v>-4.370603710412979e-05</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3999999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-2.73585319519043e-05</v>
+        <v>-2.736039459705353e-05</v>
       </c>
       <c r="JB119" t="n">
         <v>0.2599999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-6.124330684542656e-05</v>
+        <v>-6.124423816800117e-05</v>
       </c>
       <c r="JB120" t="n">
         <v>0.1199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-8.787494152784348e-05</v>
+        <v>-8.78763385117054e-05</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.02000000000000007</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.000156014459207654</v>
+        <v>-0.0001560149248689413</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.0001578782685101032</v>
+        <v>-0.0001578780356794596</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.0001492428127676249</v>
+        <v>-0.0001492416486144066</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.3</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.0001412020064890385</v>
+        <v>-0.0001412013079971075</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3</v>
